--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260805.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.85%</t>
+          <t>17.04%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>77,800,000</t>
+          <t>79,000,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.39%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,495,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>8,060,000</t>
+          <t>1,495,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.38%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>41,155,000</t>
+          <t>42,300,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,244 +814,244 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,030,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>7,160,000</t>
+          <t>1,030,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>7,160,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>3,850,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,154,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>6,154,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>158,500</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,226,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>158,500</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>2,646,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1183,232 +1183,232 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>5,330,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>7,498,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>7,498,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,587,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>172,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,312,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,312,000</t>
+          <t>670,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1430,68 +1430,68 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>650,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>624,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>1,058,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>23,694,573,460</t>
+          <t>21,568,271,007</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-4,793,582,604</t>
+          <t>-4,302,901,015</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
